--- a/testdata/opencart_logindata.xlsx
+++ b/testdata/opencart_logindata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavan\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Esh/Desktop/Esh/Opencart_AI_Playwright/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CCD88F-9D34-48AB-A36B-A56B726958D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB68BA1-A2B1-5440-83D4-1DAC205B388A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{B97F95F2-B50B-4A5D-AFCB-0992389C678D}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16360" xr2:uid="{B97F95F2-B50B-4A5D-AFCB-0992389C678D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Invalid login</t>
   </si>
   <si>
-    <t>pavanol@xyz.com</t>
-  </si>
-  <si>
     <t>test@123</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t>failure</t>
+  </si>
+  <si>
+    <t>aaa.bbb@xyz.com</t>
   </si>
 </sst>
 </file>
@@ -461,18 +461,37 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6649D996-6833-C548-BBDE-C83189B87AE7}">
+  <we:reference id="93533c7f-4dc5-468f-aba4-1c008e1a7ac8" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003101" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD8BF9D-07DD-4E1D-AF02-2D0EFDB13D0E}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.90625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" customWidth="1"/>
-    <col min="4" max="4" width="18.6328125" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="4" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -486,32 +505,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
